--- a/data/trans_camb/P15B_tráfico-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P15B_tráfico-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-21,92</t>
+          <t>-19,9</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,08</t>
+          <t>0,02</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-12,17</t>
+          <t>-11,12</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-33,11; 10,12</t>
+          <t>-33,11; 10,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-36,07; 10,45</t>
+          <t>-36,88; 9,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-43,02; -4,05</t>
+          <t>-41,6; -2,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-30,47; 10,66</t>
+          <t>-30,92; 11,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-23,24; 19,4</t>
+          <t>-26,51; 19,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-24,61; 17,26</t>
+          <t>-28,78; 16,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-23,02; 7,06</t>
+          <t>-25,27; 6,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-21,73; 8,79</t>
+          <t>-21,76; 10,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-28,23; 1,41</t>
+          <t>-26,86; 1,83</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-74,38%</t>
+          <t>-67,52%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-0,47%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-49,54%</t>
+          <t>-45,3%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-71,71; 83,88</t>
+          <t>-71,31; 75,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-78,11; 72,01</t>
+          <t>-77,23; 70,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-93,85; -4,28</t>
+          <t>-90,03; 14,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-86,43; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-65,55; 536,81</t>
+          <t>-67,91; 382,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-68,78; —</t>
+          <t>-74,1; 305,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-67,18; 55,99</t>
+          <t>-68,77; 57,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-60,95; 70,02</t>
+          <t>-58,94; 73,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-76,1; 16,64</t>
+          <t>-73,04; 15,93</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-5,29</t>
+          <t>-7,77</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,45</t>
+          <t>4,65</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-1,49</t>
+          <t>-2,72</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-31,9; 5,17</t>
+          <t>-31,88; 4,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-37,05; 3,17</t>
+          <t>-34,13; 3,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-27,51; 20,45</t>
+          <t>-29,56; 12,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-25,46; 11,75</t>
+          <t>-25,34; 10,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-23,52; 13,91</t>
+          <t>-25,18; 14,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-17,7; 24,65</t>
+          <t>-16,25; 23,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-23,2; 2,99</t>
+          <t>-24,02; 3,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-26,36; 1,77</t>
+          <t>-25,1; 1,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-16,51; 16,14</t>
+          <t>-18,93; 12,18</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-14,53%</t>
+          <t>-21,32%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-4,87%</t>
+          <t>-8,88%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-64,69; 25,9</t>
+          <t>-64,51; 24,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-75,65; 19,96</t>
+          <t>-73,29; 19,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-61,31; 103,67</t>
+          <t>-63,22; 54,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-71,33; 109,7</t>
+          <t>-67,99; 103,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-73,29; 165,31</t>
+          <t>-71,82; 164,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-58,19; 286,69</t>
+          <t>-54,43; 235,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-58,54; 16,41</t>
+          <t>-58,46; 17,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-65,91; 11,42</t>
+          <t>-64,53; 9,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-43,21; 76,91</t>
+          <t>-48,95; 58,38</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-7,44</t>
+          <t>-9,48</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-9,82</t>
+          <t>-9,9</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-10,17</t>
+          <t>-11,01</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-27,32; 16,44</t>
+          <t>-32,21; 16,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-41,34; 6,85</t>
+          <t>-40,9; 9,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-35,38; 17,03</t>
+          <t>-38,59; 13,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-19,65; 20,33</t>
+          <t>-18,64; 20,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-26,36; 15,83</t>
+          <t>-27,6; 16,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-31,29; 8,1</t>
+          <t>-30,74; 8,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-17,46; 15,21</t>
+          <t>-18,06; 14,63</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-24,43; 6,33</t>
+          <t>-27,07; 6,47</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-28,01; 6,23</t>
+          <t>-28,57; 4,92</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-21,42%</t>
+          <t>-27,28%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-45,54%</t>
+          <t>-45,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-36,17%</t>
+          <t>-39,16%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-55,56; 85,78</t>
+          <t>-59,51; 94,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-81,74; 39,89</t>
+          <t>-80,59; 52,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-72,79; 90,19</t>
+          <t>-76,52; 77,99</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-54,71; 253,99</t>
+          <t>-56,21; 240,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-77,73; 214,56</t>
+          <t>-82,15; 220,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-88,93; 154,7</t>
+          <t>-84,43; 130,86</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-45,05; 87,72</t>
+          <t>-45,0; 83,51</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-66,75; 33,96</t>
+          <t>-68,82; 38,28</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-72,27; 42,6</t>
+          <t>-72,36; 33,29</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8,84</t>
+          <t>12,3</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,33</t>
+          <t>6,42</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6,71</t>
+          <t>8,41</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-19,89; 17,03</t>
+          <t>-18,02; 17,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-21,67; 16,24</t>
+          <t>-22,38; 16,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,5; 27,37</t>
+          <t>-9,49; 30,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-21,35; 18,03</t>
+          <t>-20,75; 17,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-26,44; 10,81</t>
+          <t>-28,67; 11,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,99; 22,47</t>
+          <t>-13,46; 24,05</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-14,34; 13,24</t>
+          <t>-14,73; 12,77</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-18,74; 7,14</t>
+          <t>-18,44; 9,81</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 20,28</t>
+          <t>-6,59; 21,84</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>33,98%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-50,74; 126,58</t>
+          <t>-43,67; 135,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-56,33; 109,88</t>
+          <t>-55,71; 115,68</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-31,8; 171,12</t>
+          <t>-23,59; 194,86</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-58,83; 275,93</t>
+          <t>-61,09; 208,49</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-74,36; 177,13</t>
+          <t>-77,56; 173,61</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-36,89; 275,36</t>
+          <t>-36,59; 314,8</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-42,13; 81,4</t>
+          <t>-42,07; 83,49</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-54,73; 42,54</t>
+          <t>-53,9; 62,96</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-24,99; 127,51</t>
+          <t>-19,47; 143,19</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-5,58</t>
+          <t>-5,32</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,99</t>
+          <t>0,97</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-3,14</t>
+          <t>-3,0</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-17,71; 2,78</t>
+          <t>-17,21; 3,31</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-22,0; -0,53</t>
+          <t>-22,03; -0,65</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-16,66; 6,17</t>
+          <t>-16,81; 6,44</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 6,63</t>
+          <t>-12,59; 7,81</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-14,1; 5,34</t>
+          <t>-14,48; 5,47</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 10,99</t>
+          <t>-9,74; 10,45</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-12,72; 1,56</t>
+          <t>-11,88; 2,37</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-15,49; -0,61</t>
+          <t>-15,56; -0,42</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-11,28; 4,63</t>
+          <t>-11,54; 4,16</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-17,27%</t>
+          <t>-16,46%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-11,46%</t>
+          <t>-10,95%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-43,98; 14,76</t>
+          <t>-42,74; 13,74</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-57,0; -2,3</t>
+          <t>-55,57; -2,74</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-43,94; 22,92</t>
+          <t>-43,58; 25,03</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-42,84; 47,86</t>
+          <t>-43,35; 55,98</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-50,7; 39,07</t>
+          <t>-52,03; 35,72</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-37,16; 75,82</t>
+          <t>-35,03; 73,75</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-38,37; 7,78</t>
+          <t>-36,78; 11,36</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-48,46; -3,11</t>
+          <t>-47,54; -1,98</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-34,91; 21,38</t>
+          <t>-34,36; 18,67</t>
         </is>
       </c>
     </row>
